--- a/Dataset_LatestVersion.xlsx
+++ b/Dataset_LatestVersion.xlsx
@@ -2603,10 +2603,10 @@
         <v>258</v>
       </c>
       <c r="J17">
-        <v>0.11</v>
+        <v>0.011</v>
       </c>
       <c r="K17">
-        <v>0.22</v>
+        <v>0.022</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -2621,19 +2621,19 @@
         <v>533.3333333333333</v>
       </c>
       <c r="P17">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="Q17">
-        <v>15.6</v>
+        <v>1560</v>
       </c>
       <c r="R17">
         <v>-13.33333333333334</v>
       </c>
       <c r="S17">
-        <v>0.04139268515822508</v>
+        <v>-1.958607314841775</v>
       </c>
       <c r="T17">
-        <v>0.1097793659205434</v>
+        <v>0.01099977817874462</v>
       </c>
       <c r="U17">
         <v>3</v>
@@ -2654,10 +2654,10 @@
         <v>6.9722946790248</v>
       </c>
       <c r="AA17">
-        <v>2.255272505103306</v>
+        <v>3.255272505103306</v>
       </c>
       <c r="AB17">
-        <v>3.584289651861328</v>
+        <v>8.188689201604687</v>
       </c>
       <c r="AD17">
         <v>-3.284817638932813</v>
@@ -2689,10 +2689,10 @@
         <v>258</v>
       </c>
       <c r="J18">
-        <v>0.11</v>
+        <v>0.011</v>
       </c>
       <c r="K18">
-        <v>0.91</v>
+        <v>0.091</v>
       </c>
       <c r="L18">
         <v>727.2727272727274</v>
@@ -2707,19 +2707,19 @@
         <v>1133.333333333333</v>
       </c>
       <c r="P18">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="Q18">
-        <v>2.6</v>
+        <v>260</v>
       </c>
       <c r="R18">
         <v>-85.55555555555556</v>
       </c>
       <c r="S18">
-        <v>0.04139268515822508</v>
+        <v>-1.958607314841775</v>
       </c>
       <c r="T18">
-        <v>0.1097793659205434</v>
+        <v>0.01099977817874462</v>
       </c>
       <c r="U18">
         <v>3.861697301833718</v>
@@ -2740,10 +2740,10 @@
         <v>7.726065797132709</v>
       </c>
       <c r="AA18">
-        <v>2.255272505103306</v>
+        <v>3.255272505103306</v>
       </c>
       <c r="AB18">
-        <v>3.584289651861328</v>
+        <v>8.188689201604687</v>
       </c>
       <c r="AD18">
         <v>-5.14234727047936</v>
@@ -2775,10 +2775,10 @@
         <v>258</v>
       </c>
       <c r="J19">
-        <v>0.11</v>
+        <v>0.011</v>
       </c>
       <c r="K19">
-        <v>1.72</v>
+        <v>0.172</v>
       </c>
       <c r="L19">
         <v>1463.636363636364</v>
@@ -2793,19 +2793,19 @@
         <v>2533.333333333333</v>
       </c>
       <c r="P19">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="Q19">
-        <v>1.6</v>
+        <v>160</v>
       </c>
       <c r="R19">
         <v>-91.1111111111111</v>
       </c>
       <c r="S19">
-        <v>0.04139268515822508</v>
+        <v>-1.958607314841775</v>
       </c>
       <c r="T19">
-        <v>0.1097793659205434</v>
+        <v>0.01099977817874462</v>
       </c>
       <c r="U19">
         <v>4.165433190873625</v>
@@ -2826,10 +2826,10 @@
         <v>8.53043845712055</v>
       </c>
       <c r="AA19">
-        <v>2.255272505103306</v>
+        <v>3.255272505103306</v>
       </c>
       <c r="AB19">
-        <v>3.584289651861328</v>
+        <v>8.188689201604687</v>
       </c>
       <c r="AD19">
         <v>-5.205257058124035</v>
@@ -2861,10 +2861,10 @@
         <v>258</v>
       </c>
       <c r="J20">
-        <v>0.11</v>
+        <v>0.011</v>
       </c>
       <c r="K20">
-        <v>2.79</v>
+        <v>0.279</v>
       </c>
       <c r="L20">
         <v>2436.363636363636</v>
@@ -2879,19 +2879,19 @@
         <v>3533.333333333333</v>
       </c>
       <c r="P20">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="Q20">
-        <v>1.6</v>
+        <v>160</v>
       </c>
       <c r="R20">
         <v>-91.1111111111111</v>
       </c>
       <c r="S20">
-        <v>0.04139268515822508</v>
+        <v>-1.958607314841775</v>
       </c>
       <c r="T20">
-        <v>0.1097793659205434</v>
+        <v>0.01099977817874462</v>
       </c>
       <c r="U20">
         <v>4.386742108870564</v>
@@ -2912,10 +2912,10 @@
         <v>8.863144192016913</v>
       </c>
       <c r="AA20">
-        <v>2.255272505103306</v>
+        <v>3.255272505103306</v>
       </c>
       <c r="AB20">
-        <v>3.584289651861328</v>
+        <v>8.188689201604687</v>
       </c>
       <c r="AD20">
         <v>-5.205257058124035</v>
@@ -2947,10 +2947,10 @@
         <v>258</v>
       </c>
       <c r="J21">
-        <v>0.11</v>
+        <v>0.011</v>
       </c>
       <c r="K21">
-        <v>2.78</v>
+        <v>0.278</v>
       </c>
       <c r="L21">
         <v>2427.272727272727</v>
@@ -2965,19 +2965,19 @@
         <v>3833.333333333333</v>
       </c>
       <c r="P21">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="Q21">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="R21">
         <v>-95</v>
       </c>
       <c r="S21">
-        <v>0.04139268515822508</v>
+        <v>-1.958607314841775</v>
       </c>
       <c r="T21">
-        <v>0.1097793659205434</v>
+        <v>0.01099977817874462</v>
       </c>
       <c r="U21">
         <v>4.38511857620635</v>
@@ -2998,10 +2998,10 @@
         <v>8.944637223256409</v>
       </c>
       <c r="AA21">
-        <v>2.255272505103306</v>
+        <v>3.255272505103306</v>
       </c>
       <c r="AB21">
-        <v>3.584289651861328</v>
+        <v>8.188689201604687</v>
       </c>
       <c r="AD21">
         <v>-5.247051771840578</v>
@@ -3033,10 +3033,10 @@
         <v>258</v>
       </c>
       <c r="J22">
-        <v>0.11</v>
+        <v>0.011</v>
       </c>
       <c r="K22">
-        <v>5.79</v>
+        <v>0.579</v>
       </c>
       <c r="L22">
         <v>5163.636363636363</v>
@@ -3051,19 +3051,19 @@
         <v>4400</v>
       </c>
       <c r="P22">
-        <v>18</v>
+        <v>1800</v>
       </c>
       <c r="Q22">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="R22">
         <v>-97.2222222222222</v>
       </c>
       <c r="S22">
-        <v>0.04139268515822508</v>
+        <v>-1.958607314841775</v>
       </c>
       <c r="T22">
-        <v>0.1097793659205434</v>
+        <v>0.01099977817874462</v>
       </c>
       <c r="U22">
         <v>4.712955650552794</v>
@@ -3084,10 +3084,10 @@
         <v>9.082507013379521</v>
       </c>
       <c r="AA22">
-        <v>2.255272505103306</v>
+        <v>3.255272505103306</v>
       </c>
       <c r="AB22">
-        <v>3.584289651861328</v>
+        <v>8.188689201604687</v>
       </c>
       <c r="AD22">
         <v>-5.270172937511671</v>
